--- a/content/dd-content-template.xlsx
+++ b/content/dd-content-template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="20835" windowHeight="11655" activeTab="1"/>
+    <workbookView windowWidth="16800" windowHeight="11655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="填写说明" sheetId="1" r:id="rId1"/>
@@ -1759,8 +1759,8 @@
         <v>21</v>
       </c>
       <c r="D3" t="str">
-        <f>_xlfn.DISPIMG("ID_3C71F5DCDA0543389D016E01273F52B7",1)</f>
-        <v>=DISPIMG("ID_3C71F5DCDA0543389D016E01273F52B7",1)</v>
+        <f>_xlfn.DISPIMG("ID_BB5BA37AD503460C9AF150B7472EC82B",1)</f>
+        <v>=DISPIMG("ID_BB5BA37AD503460C9AF150B7472EC82B",1)</v>
       </c>
     </row>
     <row r="4" ht="127.05" customHeight="1" spans="1:4">
@@ -1789,8 +1789,8 @@
         <v>27</v>
       </c>
       <c r="D5" t="str">
-        <f>_xlfn.DISPIMG("ID_479F54CB889E4BAD9E253AEB6ADACDFD",1)</f>
-        <v>=DISPIMG("ID_479F54CB889E4BAD9E253AEB6ADACDFD",1)</v>
+        <f>_xlfn.DISPIMG("ID_F000C0E578BE4C649E624AF44BA557BA",1)</f>
+        <v>=DISPIMG("ID_F000C0E578BE4C649E624AF44BA557BA",1)</v>
       </c>
     </row>
     <row r="6" ht="90" customHeight="1" spans="1:4">
@@ -1819,8 +1819,8 @@
         <v>33</v>
       </c>
       <c r="D7" t="str">
-        <f>_xlfn.DISPIMG("ID_BB5BA37AD503460C9AF150B7472EC82B",1)</f>
-        <v>=DISPIMG("ID_BB5BA37AD503460C9AF150B7472EC82B",1)</v>
+        <f>_xlfn.DISPIMG("ID_3C71F5DCDA0543389D016E01273F52B7",1)</f>
+        <v>=DISPIMG("ID_3C71F5DCDA0543389D016E01273F52B7",1)</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1" spans="1:4">
@@ -1834,15 +1834,15 @@
         <v>36</v>
       </c>
       <c r="D8" t="str">
-        <f>_xlfn.DISPIMG("ID_F000C0E578BE4C649E624AF44BA557BA",1)</f>
-        <v>=DISPIMG("ID_F000C0E578BE4C649E624AF44BA557BA",1)</v>
+        <f>_xlfn.DISPIMG("ID_479F54CB889E4BAD9E253AEB6ADACDFD",1)</f>
+        <v>=DISPIMG("ID_479F54CB889E4BAD9E253AEB6ADACDFD",1)</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:D1 A2:C8" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:C8 A1:D1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
